--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1442,7 +1442,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1914,7 +1914,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2032,7 +2032,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2150,7 +2150,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2268,7 +2268,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2445,7 +2445,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2563,7 +2563,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2858,7 +2858,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2976,7 +2976,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
